--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/VR MENSAL 05.2025.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/VR MENSAL 05.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08174652-F090-4C56-A5C1-8FC22ACC845D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6AE20-46F7-4BBE-8B38-7A89D540F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,10 +19,19 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VR MENSAL 05.2025'!$A$2:$I$1901</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -31,8 +40,43 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Antonio Dantas</author>
+  </authors>
+  <commentList>
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{849EF872-F5CC-4AE0-987B-BDFC2CA14A4B}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Antonio Dantas:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Quando a despesa é registrada
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
   <si>
     <t>Matricula</t>
   </si>
@@ -135,6 +179,12 @@
   <si>
     <t>Sindicato do Colaborador</t>
   </si>
+  <si>
+    <t>80% do TOTAL</t>
+  </si>
+  <si>
+    <t>20% do TOTAL</t>
+  </si>
 </sst>
 </file>
 
@@ -146,7 +196,7 @@
     <numFmt numFmtId="164" formatCode="000000"/>
     <numFmt numFmtId="165" formatCode="mm/yyyy"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -235,6 +285,19 @@
       <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -730,7 +793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1901"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -804,6 +867,7 @@
         <v>37.5</v>
       </c>
       <c r="G3" s="6">
+        <f>F3*E3</f>
         <v>825</v>
       </c>
       <c r="H3" s="6">
@@ -821,8 +885,12 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
+      <c r="H4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
@@ -21761,6 +21829,7 @@
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;KFF0000 Classificação: Restrito&amp;1#_x000D_</oddHeader>
   </headerFooter>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -21871,6 +21940,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <NomeCompleto xmlns="14b3b570-1645-47e5-a265-7d995086a9a7" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="14b3b570-1645-47e5-a265-7d995086a9a7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="497f2ec6-c6e6-480c-8663-86384358ee29" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101007D55C8326FDE94429C494C5C6510D6D9" ma:contentTypeVersion="18" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9791db0fa2d45dddec2a31306127fcee">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="14b3b570-1645-47e5-a265-7d995086a9a7" xmlns:ns3="497f2ec6-c6e6-480c-8663-86384358ee29" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2ec7d34f13e4e836e7d82ffa9ba888" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -22130,30 +22222,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <NomeCompleto xmlns="14b3b570-1645-47e5-a265-7d995086a9a7" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="14b3b570-1645-47e5-a265-7d995086a9a7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="497f2ec6-c6e6-480c-8663-86384358ee29" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33415E1-8AC5-4A12-8C87-439A5F77C122}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B238700B-EFB8-41B4-A07A-8B3D5DD77456}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="14b3b570-1645-47e5-a265-7d995086a9a7"/>
+    <ds:schemaRef ds:uri="497f2ec6-c6e6-480c-8663-86384358ee29"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24210C09-53F7-4283-AA96-F1FA1DE49F41}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -22171,24 +22260,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B238700B-EFB8-41B4-A07A-8B3D5DD77456}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="14b3b570-1645-47e5-a265-7d995086a9a7"/>
-    <ds:schemaRef ds:uri="497f2ec6-c6e6-480c-8663-86384358ee29"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33415E1-8AC5-4A12-8C87-439A5F77C122}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Desafio 4 - Vale Refeição/Desafio 4 - Dados/VR MENSAL 05.2025.xlsx
+++ b/Desafio 4 - Vale Refeição/Desafio 4 - Dados/VR MENSAL 05.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Cursos e Treinamentos\Cientista de Dados\Treinamento Python\I2A2\Desafios\Desafio 4 - Vale Refeição\Desafio 4 - Dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B6AE20-46F7-4BBE-8B38-7A89D540F1BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF1DD3F-A191-4DD6-AC32-4EA74FEC4D1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,19 +19,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'VR MENSAL 05.2025'!$A$2:$I$1901</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -40,43 +31,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Antonio Dantas</author>
-  </authors>
-  <commentList>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{849EF872-F5CC-4AE0-987B-BDFC2CA14A4B}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Segoe UI"/>
-            <charset val="1"/>
-          </rPr>
-          <t>Antonio Dantas:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Segoe UI"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-Quando a despesa é registrada
-</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>Matricula</t>
   </si>
@@ -179,12 +135,6 @@
   <si>
     <t>Sindicato do Colaborador</t>
   </si>
-  <si>
-    <t>80% do TOTAL</t>
-  </si>
-  <si>
-    <t>20% do TOTAL</t>
-  </si>
 </sst>
 </file>
 
@@ -196,7 +146,7 @@
     <numFmt numFmtId="164" formatCode="000000"/>
     <numFmt numFmtId="165" formatCode="mm/yyyy"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -279,26 +229,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Segoe UI"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -370,7 +300,7 @@
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -468,12 +398,6 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -793,13 +717,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1901"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.5703125" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="92.5703125" style="7" customWidth="1"/>
     <col min="4" max="4" width="14" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" style="7" bestFit="1" customWidth="1"/>
@@ -851,13 +775,13 @@
       <c r="A3" s="2">
         <v>34914</v>
       </c>
-      <c r="B3" s="38">
+      <c r="B3" s="4">
         <v>45505</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="39">
+      <c r="D3" s="5">
         <v>45778</v>
       </c>
       <c r="E3" s="6">
@@ -867,7 +791,6 @@
         <v>37.5</v>
       </c>
       <c r="G3" s="6">
-        <f>F3*E3</f>
         <v>825</v>
       </c>
       <c r="H3" s="6">
@@ -885,12 +808,8 @@
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
@@ -21829,7 +21748,6 @@
   <headerFooter>
     <oddHeader>&amp;L&amp;"Calibri"&amp;10&amp;KFF0000 Classificação: Restrito&amp;1#_x000D_</oddHeader>
   </headerFooter>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -21940,15 +21858,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -21960,6 +21869,15 @@
     <TaxCatchAll xmlns="497f2ec6-c6e6-480c-8663-86384358ee29" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22223,14 +22141,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33415E1-8AC5-4A12-8C87-439A5F77C122}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B238700B-EFB8-41B4-A07A-8B3D5DD77456}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -22238,6 +22148,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="14b3b570-1645-47e5-a265-7d995086a9a7"/>
     <ds:schemaRef ds:uri="497f2ec6-c6e6-480c-8663-86384358ee29"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33415E1-8AC5-4A12-8C87-439A5F77C122}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
